--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="143">
   <si>
     <t>Property</t>
   </si>
@@ -57,10 +57,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T07:40:29+00:00</t>
+    <t>2026-08-24T13:49:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,13 +117,10 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -344,7 +344,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/QuelleKlinischesBezugsdatum|2027.0.0</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/QuelleKlinischesBezugsdatum</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -664,98 +664,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -817,7 +819,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="91.38671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="83.859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -941,10 +943,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -970,7 +972,7 @@
         <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M2" t="s" s="2">
         <v>80</v>
@@ -1024,7 +1026,7 @@
         <v>76</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>77</v>
@@ -1170,7 +1172,7 @@
         <v>90</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
         <v>80</v>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:49:26+00:00</t>
+    <t>2026-08-28T09:59:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:59:02+00:00</t>
+    <t>2026-08-28T10:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:19:24+00:00</t>
+    <t>2026-09-01T07:28:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T07:28:55+00:00</t>
+    <t>2026-09-01T08:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:17:52+00:00</t>
+    <t>2026-09-01T11:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:26:20+00:00</t>
+    <t>2026-09-01T11:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:37:07+00:00</t>
+    <t>2026-09-01T11:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:44:40+00:00</t>
+    <t>2026-09-01T12:05:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:05:15+00:00</t>
+    <t>2026-09-01T12:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:12:27+00:00</t>
+    <t>2026-09-01T12:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:31:59+00:00</t>
+    <t>2026-09-01T12:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:37:11+00:00</t>
+    <t>2026-09-01T12:41:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:41:57+00:00</t>
+    <t>2026-09-01T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:58:26+00:00</t>
+    <t>2026-09-01T13:38:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:38:20+00:00</t>
+    <t>2026-09-01T13:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:44:38+00:00</t>
+    <t>2026-09-01T14:35:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:35:41+00:00</t>
+    <t>2026-09-01T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:11:46+00:00</t>
+    <t>2026-09-01T15:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:27:37+00:00</t>
+    <t>2026-09-01T15:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:32:49+00:00</t>
+    <t>2026-09-01T15:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:38:53+00:00</t>
+    <t>2026-09-01T16:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:17:13+00:00</t>
+    <t>2026-09-01T16:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:23:29+00:00</t>
+    <t>2026-09-02T06:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:57:39+00:00</t>
+    <t>2026-09-02T07:24:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:24:40+00:00</t>
+    <t>2026-09-02T08:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T08:07:59+00:00</t>
+    <t>2026-09-02T09:10:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:10:52+00:00</t>
+    <t>2026-09-02T09:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:21:54+00:00</t>
+    <t>2026-09-02T10:32:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:32:32+00:00</t>
+    <t>2026-09-02T10:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:47:13+00:00</t>
+    <t>2026-09-02T11:41:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
+++ b/branches/ig-publisher-migration/StructureDefinition-mii-ex-labor-quelle-klinisches-bezugsdatum.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T11:41:16+00:00</t>
+    <t>2026-09-02T11:51:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
